--- a/data-raw/metadata/clear_years_to_include_metadata.xlsx
+++ b/data-raw/metadata/clear_years_to_include_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Badhia\Documents\git\jpe-clear-adult-edi\data-raw\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE739190-CBD7-403C-94EF-0D633447BA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C39D70-E7A4-49EB-898B-2462D65F9C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6400" yWindow="680" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attribute" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
   <si>
     <t xml:space="preserve">attribute_name </t>
   </si>
@@ -119,6 +119,12 @@
   </si>
   <si>
     <t>2024</t>
+  </si>
+  <si>
+    <t>data_type</t>
+  </si>
+  <si>
+    <t>Type of data collected. Levels = c("passage", redd")</t>
   </si>
 </sst>
 </file>
@@ -640,11 +646,21 @@
       <c r="Z4" s="7"/>
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="4"/>
+      <c r="A5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>25</v>
+      </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>

--- a/data-raw/metadata/clear_years_to_include_metadata.xlsx
+++ b/data-raw/metadata/clear_years_to_include_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Badhia\Documents\git\jpe-clear-adult-edi\data-raw\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C39D70-E7A4-49EB-898B-2462D65F9C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D70A70C-FE96-4861-A38C-9AA5D74C1EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6400" yWindow="680" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1640" yWindow="2490" windowWidth="15620" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attribute" sheetId="1" r:id="rId1"/>
@@ -91,9 +91,6 @@
     <t>Year of  adult data collection</t>
   </si>
   <si>
-    <t>removed</t>
-  </si>
-  <si>
     <t>Indicates if year should be removed from analysis if TRUE</t>
   </si>
   <si>
@@ -125,6 +122,9 @@
   </si>
   <si>
     <t>Type of data collected. Levels = c("passage", redd")</t>
+  </si>
+  <si>
+    <t>remove</t>
   </si>
 </sst>
 </file>
@@ -523,7 +523,7 @@
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>20</v>
@@ -532,7 +532,7 @@
         <v>13</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>14</v>
@@ -550,10 +550,10 @@
       <c r="J2" s="15"/>
       <c r="K2" s="14"/>
       <c r="L2" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M2" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
@@ -571,19 +571,19 @@
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="C3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>24</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>25</v>
       </c>
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
@@ -609,19 +609,19 @@
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>27</v>
+      <c r="C4" s="13" t="s">
+        <v>22</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="D4" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>24</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>25</v>
       </c>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
@@ -647,19 +647,19 @@
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>32</v>
+      <c r="C5" s="4" t="s">
+        <v>22</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>24</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>25</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
